--- a/data/b2_candoi/B2 Candói 08-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 08-2026.xlsx
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1005.24</v>
+        <v>1045.27</v>
       </c>
     </row>
     <row r="3">
@@ -4909,97 +4909,97 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>58512.78</v>
+        <v>57474.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46239</v>
+        <v>46243</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1131.61</v>
+        <v>3562.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3567.21</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3200</v>
+        <v>969.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>942.9299999999999</v>
+        <v>1127.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1996.76</v>
+        <v>9208.200000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5008,75 +5008,75 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8314.879999999999</v>
+        <v>1064.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1832.67</v>
+        <v>3640.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1001.46</v>
+        <v>3420.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3380.43</v>
+        <v>20631.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5085,29 +5085,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1391.13</v>
+        <v>1402.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20442.79</v>
+        <v>1428.96</v>
       </c>
     </row>
     <row r="15">
@@ -5125,43 +5125,43 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3657.73</v>
+        <v>3309.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>8250</v>
+        <v>1931.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1122.8</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3732.47</v>
+        <v>3539.61</v>
       </c>
     </row>
     <row r="19">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>482.21</v>
+        <v>455.68</v>
       </c>
     </row>
   </sheetData>
